--- a/Docs/BOM.xlsx
+++ b/Docs/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\6-DOF-Robot-Arm\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8614DDD-FCB3-4C19-8CEF-CA3D389016DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2630FB33-DE55-4950-9503-B3A479F7ED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>名稱</t>
   </si>
@@ -59,15 +59,6 @@
     <t>杜邦4pin接頭</t>
   </si>
   <si>
-    <t>數排</t>
-  </si>
-  <si>
-    <t>四種顏色數條</t>
-  </si>
-  <si>
-    <t>數個</t>
-  </si>
-  <si>
     <t>M5螺絲+羅母</t>
   </si>
   <si>
@@ -77,9 +68,6 @@
     <t>M3螺絲+羅母</t>
   </si>
   <si>
-    <t>大量</t>
-  </si>
-  <si>
     <t>鋁擠型2020</t>
   </si>
   <si>
@@ -111,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Locking Assembly</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Z21-ID 8 * OD 18 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -229,6 +213,25 @@
   <si>
     <t>NEMA14L20</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 colors servral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plenty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expansion Bushing</t>
   </si>
 </sst>
 </file>
@@ -564,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="56.7109375" customWidth="1"/>
@@ -582,22 +585,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -608,10 +611,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -622,10 +625,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -636,7 +639,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>6009</v>
@@ -650,10 +653,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
@@ -664,13 +667,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="2"/>
@@ -678,10 +681,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -692,13 +695,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="2"/>
@@ -706,13 +709,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="2"/>
@@ -720,10 +723,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="3">
-        <v>6007</v>
+        <v>23</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -734,13 +737,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="B12" s="3">
+        <v>6007</v>
       </c>
       <c r="C12" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="2"/>
@@ -748,13 +751,13 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="2"/>
@@ -762,10 +765,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -776,49 +779,50 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -828,35 +832,37 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="C21" s="3">
         <v>1</v>
       </c>
@@ -865,85 +871,89 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="3"/>
-      <c r="C22" s="3" t="s">
-        <v>7</v>
+      <c r="C22" s="3">
+        <v>1</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="2"/>
-      <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="2"/>
+      <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="A29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="1:10">
@@ -967,6 +977,13 @@
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
